--- a/Arquivos/nao_atualizaveis/Ativo_PROPAG NI/Discagem_propag_NOVA IGUAÇU.xlsx
+++ b/Arquivos/nao_atualizaveis/Ativo_PROPAG NI/Discagem_propag_NOVA IGUAÇU.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\FIRJAN\Dashboard\dashboard-firjan\Arquivos\nao_atualizaveis\Ativo_PROPAG NI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87DA85BC-A880-45D5-B996-5BF2C2BED942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19599E5B-A757-44DA-BF43-9BA534767345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamadas_30-09-2026_112538" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="51">
   <si>
     <t>DATA</t>
   </si>
@@ -130,9 +130,6 @@
     <t>15872708700</t>
   </si>
   <si>
-    <t>Nova Iguaçu</t>
-  </si>
-  <si>
     <t>(21) 96673-3106</t>
   </si>
   <si>
@@ -161,6 +158,24 @@
   </si>
   <si>
     <t>22277911798</t>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>Nova Iguacu</t>
+  </si>
+  <si>
+    <t>751</t>
+  </si>
+  <si>
+    <t>1517</t>
+  </si>
+  <si>
+    <t>2828</t>
+  </si>
+  <si>
+    <t>3697</t>
   </si>
 </sst>
 </file>
@@ -210,9 +225,9 @@
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="21" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -527,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -548,7 +563,7 @@
     <col min="17" max="17" width="18.5546875" customWidth="1"/>
     <col min="18" max="18" width="18.77734375" customWidth="1"/>
     <col min="19" max="19" width="24.109375" customWidth="1"/>
-    <col min="20" max="20" width="14" style="8" customWidth="1"/>
+    <col min="20" max="20" width="14" style="7" customWidth="1"/>
     <col min="21" max="21" width="16" customWidth="1"/>
     <col min="22" max="22" width="18" customWidth="1"/>
   </cols>
@@ -611,7 +626,7 @@
       <c r="S1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="7" t="s">
+      <c r="T1" s="6" t="s">
         <v>19</v>
       </c>
       <c r="U1" s="4" t="s">
@@ -631,8 +646,8 @@
       <c r="C2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="8">
-        <v>357</v>
+      <c r="D2" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="F2">
         <v>2760344813</v>
@@ -664,14 +679,14 @@
       <c r="S2" t="s">
         <v>23</v>
       </c>
-      <c r="T2" s="7">
-        <v>357</v>
+      <c r="T2" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="U2" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="V2" s="4" t="s">
-        <v>35</v>
+      <c r="V2" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -684,8 +699,8 @@
       <c r="C3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="8">
-        <v>357</v>
+      <c r="D3" s="8" t="s">
+        <v>45</v>
       </c>
       <c r="F3">
         <v>2760344860</v>
@@ -717,14 +732,14 @@
       <c r="S3" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="7">
-        <v>357</v>
+      <c r="T3" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="V3" s="4" t="s">
-        <v>35</v>
+      <c r="V3" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.3">
@@ -737,8 +752,8 @@
       <c r="C4" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="8">
-        <v>751</v>
+      <c r="D4" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="F4">
         <v>2757441143</v>
@@ -750,7 +765,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J4" t="s">
         <v>31</v>
@@ -773,14 +788,14 @@
       <c r="S4" s="3">
         <v>4.6296296296296287E-5</v>
       </c>
-      <c r="T4" s="7">
-        <v>751</v>
+      <c r="T4" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="U4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="V4" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.3">
@@ -793,8 +808,8 @@
       <c r="C5" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="8">
-        <v>751</v>
+      <c r="D5" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="F5">
         <v>2757441214</v>
@@ -806,7 +821,7 @@
         <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J5" t="s">
         <v>31</v>
@@ -829,14 +844,14 @@
       <c r="S5" s="3">
         <v>5.7870370370370373E-5</v>
       </c>
-      <c r="T5" s="7">
-        <v>751</v>
+      <c r="T5" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="V5" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="V5" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.3">
@@ -849,8 +864,8 @@
       <c r="C6" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="8">
-        <v>751</v>
+      <c r="D6" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="F6">
         <v>2757441275</v>
@@ -862,7 +877,7 @@
         <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J6" t="s">
         <v>31</v>
@@ -885,14 +900,14 @@
       <c r="S6" s="3">
         <v>3.4722222222222222E-5</v>
       </c>
-      <c r="T6" s="7">
-        <v>751</v>
+      <c r="T6" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="U6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="V6" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="V6" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.3">
@@ -905,8 +920,8 @@
       <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="8">
-        <v>1517</v>
+      <c r="D7" s="8" t="s">
+        <v>48</v>
       </c>
       <c r="F7">
         <v>2771687506</v>
@@ -918,7 +933,7 @@
         <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="J7" t="s">
         <v>31</v>
@@ -941,14 +956,14 @@
       <c r="S7" s="3">
         <v>1.157407407407407E-4</v>
       </c>
-      <c r="T7" s="7">
-        <v>1517</v>
+      <c r="T7" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="V7" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
+      </c>
+      <c r="V7" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.3">
@@ -961,8 +976,8 @@
       <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="8">
-        <v>751</v>
+      <c r="D8" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="F8">
         <v>2789637080</v>
@@ -974,7 +989,7 @@
         <v>30</v>
       </c>
       <c r="I8" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J8" t="s">
         <v>31</v>
@@ -997,14 +1012,14 @@
       <c r="S8" t="s">
         <v>23</v>
       </c>
-      <c r="T8" s="7">
-        <v>751</v>
+      <c r="T8" s="5" t="s">
+        <v>47</v>
       </c>
       <c r="U8" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="V8" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="V8" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.3">
@@ -1017,8 +1032,8 @@
       <c r="C9" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="8">
-        <v>2828</v>
+      <c r="D9" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="F9">
         <v>2765229192</v>
@@ -1030,7 +1045,7 @@
         <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J9" t="s">
         <v>31</v>
@@ -1053,14 +1068,14 @@
       <c r="S9" t="s">
         <v>23</v>
       </c>
-      <c r="T9" s="7">
-        <v>2828</v>
+      <c r="T9" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="V9" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="V9" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.3">
@@ -1073,8 +1088,8 @@
       <c r="C10" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="8">
-        <v>2828</v>
+      <c r="D10" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="F10">
         <v>2761580385</v>
@@ -1086,7 +1101,7 @@
         <v>30</v>
       </c>
       <c r="I10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J10" t="s">
         <v>31</v>
@@ -1109,14 +1124,14 @@
       <c r="S10" s="3">
         <v>5.7870370370370373E-5</v>
       </c>
-      <c r="T10" s="7">
-        <v>2828</v>
+      <c r="T10" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="U10" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="V10" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="V10" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.3">
@@ -1129,8 +1144,8 @@
       <c r="C11" t="s">
         <v>25</v>
       </c>
-      <c r="D11" s="8">
-        <v>2828</v>
+      <c r="D11" s="8" t="s">
+        <v>49</v>
       </c>
       <c r="F11">
         <v>2761580435</v>
@@ -1142,7 +1157,7 @@
         <v>30</v>
       </c>
       <c r="I11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J11" t="s">
         <v>31</v>
@@ -1165,14 +1180,14 @@
       <c r="S11" s="3">
         <v>1.157407407407407E-4</v>
       </c>
-      <c r="T11" s="7">
-        <v>2828</v>
+      <c r="T11" s="5" t="s">
+        <v>49</v>
       </c>
       <c r="U11" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="V11" s="6" t="s">
-        <v>35</v>
+        <v>41</v>
+      </c>
+      <c r="V11" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.3">
@@ -1185,8 +1200,8 @@
       <c r="C12" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="8">
-        <v>3697</v>
+      <c r="D12" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="F12">
         <v>2768060011</v>
@@ -1198,7 +1213,7 @@
         <v>30</v>
       </c>
       <c r="I12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J12" t="s">
         <v>31</v>
@@ -1221,14 +1236,14 @@
       <c r="S12" s="3">
         <v>1.157407407407407E-5</v>
       </c>
-      <c r="T12" s="7">
-        <v>3697</v>
+      <c r="T12" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="U12" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="V12" s="6" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="V12" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.3">
@@ -1241,8 +1256,8 @@
       <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="8">
-        <v>3697</v>
+      <c r="D13" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="F13">
         <v>2768060064</v>
@@ -1254,7 +1269,7 @@
         <v>30</v>
       </c>
       <c r="I13" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J13" t="s">
         <v>31</v>
@@ -1274,14 +1289,14 @@
       <c r="S13" t="s">
         <v>23</v>
       </c>
-      <c r="T13" s="7">
-        <v>3697</v>
+      <c r="T13" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="U13" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="V13" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.3">
@@ -1294,8 +1309,8 @@
       <c r="C14" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="8">
-        <v>3697</v>
+      <c r="D14" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="F14">
         <v>2768060118</v>
@@ -1307,7 +1322,7 @@
         <v>30</v>
       </c>
       <c r="I14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J14" t="s">
         <v>31</v>
@@ -1330,14 +1345,14 @@
       <c r="S14" s="3">
         <v>1.157407407407407E-5</v>
       </c>
-      <c r="T14" s="7">
-        <v>3697</v>
+      <c r="T14" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="U14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="V14" s="6" t="s">
-        <v>35</v>
+        <v>44</v>
+      </c>
+      <c r="V14" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.3">
@@ -1350,8 +1365,8 @@
       <c r="C15" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="8">
-        <v>3697</v>
+      <c r="D15" s="8" t="s">
+        <v>50</v>
       </c>
       <c r="F15">
         <v>2768060172</v>
@@ -1363,7 +1378,7 @@
         <v>30</v>
       </c>
       <c r="I15" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J15" t="s">
         <v>31</v>
@@ -1383,14 +1398,824 @@
       <c r="S15" t="s">
         <v>23</v>
       </c>
-      <c r="T15" s="7">
-        <v>3697</v>
+      <c r="T15" s="5" t="s">
+        <v>50</v>
       </c>
       <c r="U15" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V15" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>46295.391469907408</v>
+      </c>
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="V15" s="4" t="s">
+      <c r="F16">
+        <v>2760407917</v>
+      </c>
+      <c r="G16" s="2">
+        <v>179077102380021</v>
+      </c>
+      <c r="H16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" t="s">
+        <v>31</v>
+      </c>
+      <c r="K16" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16">
+        <v>19</v>
+      </c>
+      <c r="R16" s="3">
+        <v>9.2592592592592588E-5</v>
+      </c>
+      <c r="S16" t="s">
+        <v>23</v>
+      </c>
+      <c r="T16" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U16" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="V16" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46295.39199074074</v>
+      </c>
+      <c r="B17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17">
+        <v>2760407962</v>
+      </c>
+      <c r="G17" s="2">
+        <v>179077106880921</v>
+      </c>
+      <c r="H17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" t="s">
+        <v>31</v>
+      </c>
+      <c r="K17" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17">
+        <v>16</v>
+      </c>
+      <c r="R17" s="3">
+        <v>3.0092592592592589E-4</v>
+      </c>
+      <c r="S17" s="3">
+        <v>2.0833333333333329E-4</v>
+      </c>
+      <c r="T17" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="V17" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46295.393229166657</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s">
+        <v>25</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18">
+        <v>2789699961</v>
+      </c>
+      <c r="G18" s="2">
+        <v>179077117583671</v>
+      </c>
+      <c r="H18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18">
+        <v>19</v>
+      </c>
+      <c r="R18" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S18" t="s">
+        <v>23</v>
+      </c>
+      <c r="T18" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="U18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V18" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>46295.393726851849</v>
+      </c>
+      <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19">
+        <v>2757504345</v>
+      </c>
+      <c r="G19" s="2">
+        <v>179077121884561</v>
+      </c>
+      <c r="H19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s">
         <v>35</v>
+      </c>
+      <c r="J19" t="s">
+        <v>31</v>
+      </c>
+      <c r="K19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="N19" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19">
+        <v>16</v>
+      </c>
+      <c r="R19" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="S19" s="3">
+        <v>2.314814814814815E-5</v>
+      </c>
+      <c r="T19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="U19" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V19" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>46295.394618055558</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20">
+        <v>2757504422</v>
+      </c>
+      <c r="G20" s="2">
+        <v>179077129586231</v>
+      </c>
+      <c r="H20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" t="s">
+        <v>31</v>
+      </c>
+      <c r="K20" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" t="s">
+        <v>32</v>
+      </c>
+      <c r="N20" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20">
+        <v>16</v>
+      </c>
+      <c r="R20" s="3">
+        <v>3.7037037037037041E-4</v>
+      </c>
+      <c r="S20" s="3">
+        <v>1.041666666666667E-4</v>
+      </c>
+      <c r="T20" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="U20" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>46295.395648148151</v>
+      </c>
+      <c r="B21" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" t="s">
+        <v>25</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F21">
+        <v>2771750677</v>
+      </c>
+      <c r="G21" s="2">
+        <v>179077138488381</v>
+      </c>
+      <c r="H21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" t="s">
+        <v>31</v>
+      </c>
+      <c r="K21" t="s">
+        <v>29</v>
+      </c>
+      <c r="N21" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21">
+        <v>19</v>
+      </c>
+      <c r="R21" s="3">
+        <v>3.2407407407407412E-4</v>
+      </c>
+      <c r="S21" t="s">
+        <v>23</v>
+      </c>
+      <c r="T21" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="U21" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="V21" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>46295.397361111107</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22">
+        <v>2771750826</v>
+      </c>
+      <c r="G22" s="2">
+        <v>179077153291941</v>
+      </c>
+      <c r="H22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" t="s">
+        <v>37</v>
+      </c>
+      <c r="J22" t="s">
+        <v>31</v>
+      </c>
+      <c r="K22" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22">
+        <v>19</v>
+      </c>
+      <c r="R22" s="3">
+        <v>3.5879629629629629E-4</v>
+      </c>
+      <c r="S22" t="s">
+        <v>23</v>
+      </c>
+      <c r="T22" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="U22" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="V22" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>46295.398356481477</v>
+      </c>
+      <c r="B23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F23">
+        <v>2771750911</v>
+      </c>
+      <c r="G23" s="2">
+        <v>179077161894251</v>
+      </c>
+      <c r="H23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" t="s">
+        <v>37</v>
+      </c>
+      <c r="J23" t="s">
+        <v>31</v>
+      </c>
+      <c r="K23" t="s">
+        <v>29</v>
+      </c>
+      <c r="N23" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23">
+        <v>19</v>
+      </c>
+      <c r="R23" s="3">
+        <v>4.1666666666666669E-4</v>
+      </c>
+      <c r="S23" t="s">
+        <v>23</v>
+      </c>
+      <c r="T23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="U23" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="V23" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>46295.399293981478</v>
+      </c>
+      <c r="B24" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" t="s">
+        <v>25</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F24">
+        <v>2761643683</v>
+      </c>
+      <c r="G24" s="2">
+        <v>179077169995851</v>
+      </c>
+      <c r="H24" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" t="s">
+        <v>42</v>
+      </c>
+      <c r="J24" t="s">
+        <v>31</v>
+      </c>
+      <c r="K24" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24">
+        <v>16</v>
+      </c>
+      <c r="R24" s="3">
+        <v>1.041666666666667E-4</v>
+      </c>
+      <c r="S24" t="s">
+        <v>23</v>
+      </c>
+      <c r="T24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="U24" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="V24" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
+        <v>46295.400046296287</v>
+      </c>
+      <c r="B25" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F25">
+        <v>2768123267</v>
+      </c>
+      <c r="G25" s="2">
+        <v>179077176496851</v>
+      </c>
+      <c r="H25" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" t="s">
+        <v>31</v>
+      </c>
+      <c r="K25" t="s">
+        <v>29</v>
+      </c>
+      <c r="N25" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25">
+        <v>19</v>
+      </c>
+      <c r="R25" s="3">
+        <v>4.6296296296296287E-5</v>
+      </c>
+      <c r="S25" t="s">
+        <v>23</v>
+      </c>
+      <c r="T25" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="U25" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="V25" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>46295.400613425933</v>
+      </c>
+      <c r="B26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F26">
+        <v>2768123317</v>
+      </c>
+      <c r="G26" s="2">
+        <v>179077181397651</v>
+      </c>
+      <c r="H26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" t="s">
+        <v>43</v>
+      </c>
+      <c r="J26" t="s">
+        <v>31</v>
+      </c>
+      <c r="K26" t="s">
+        <v>29</v>
+      </c>
+      <c r="N26" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26">
+        <v>19</v>
+      </c>
+      <c r="R26" s="3">
+        <v>4.6296296296296287E-5</v>
+      </c>
+      <c r="S26" t="s">
+        <v>23</v>
+      </c>
+      <c r="T26" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="U26" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="V26" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>46296.400462962964</v>
+      </c>
+      <c r="B27" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" t="s">
+        <v>25</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27">
+        <v>2760495095</v>
+      </c>
+      <c r="G27" s="2">
+        <v>179085820071521</v>
+      </c>
+      <c r="H27" t="s">
+        <v>30</v>
+      </c>
+      <c r="I27" t="s">
+        <v>33</v>
+      </c>
+      <c r="J27" t="s">
+        <v>31</v>
+      </c>
+      <c r="K27" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" t="s">
+        <v>26</v>
+      </c>
+      <c r="N27" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27">
+        <v>16</v>
+      </c>
+      <c r="R27" s="3">
+        <v>3.2407407407407406E-4</v>
+      </c>
+      <c r="S27" s="3">
+        <v>2.3148148148148149E-4</v>
+      </c>
+      <c r="T27" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U27" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="V27" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>46296.401261574072</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>25</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28">
+        <v>2789787055</v>
+      </c>
+      <c r="G28" s="2">
+        <v>179085826972561</v>
+      </c>
+      <c r="H28" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" t="s">
+        <v>39</v>
+      </c>
+      <c r="J28" t="s">
+        <v>31</v>
+      </c>
+      <c r="K28" t="s">
+        <v>29</v>
+      </c>
+      <c r="N28" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28">
+        <v>19</v>
+      </c>
+      <c r="R28" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S28" t="s">
+        <v>23</v>
+      </c>
+      <c r="T28" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="U28" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V28" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A29" s="1">
+        <v>46296.410717592589</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F29">
+        <v>2760495980</v>
+      </c>
+      <c r="G29" s="2">
+        <v>179085908683991</v>
+      </c>
+      <c r="H29" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" t="s">
+        <v>33</v>
+      </c>
+      <c r="J29" t="s">
+        <v>31</v>
+      </c>
+      <c r="K29" t="s">
+        <v>29</v>
+      </c>
+      <c r="N29" t="s">
+        <v>27</v>
+      </c>
+      <c r="O29">
+        <v>19</v>
+      </c>
+      <c r="R29" s="3">
+        <v>6.9444444444444444E-5</v>
+      </c>
+      <c r="S29" t="s">
+        <v>23</v>
+      </c>
+      <c r="T29" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="U29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="V29" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="A30" s="1">
+        <v>46296.411261574074</v>
+      </c>
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F30">
+        <v>2789787919</v>
+      </c>
+      <c r="G30" s="2">
+        <v>179085913384971</v>
+      </c>
+      <c r="H30" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" t="s">
+        <v>39</v>
+      </c>
+      <c r="J30" t="s">
+        <v>31</v>
+      </c>
+      <c r="K30" t="s">
+        <v>29</v>
+      </c>
+      <c r="N30" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30">
+        <v>19</v>
+      </c>
+      <c r="R30" s="3">
+        <v>5.7870370370370373E-5</v>
+      </c>
+      <c r="S30" t="s">
+        <v>23</v>
+      </c>
+      <c r="T30" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="U30" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="V30" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
